--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_OPOSITA MARÍN ENCE PEIXEGALEGO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_OPOSITA MARÍN ENCE PEIXEGALEGO.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>115.4336</v>
+        <v>126.9517</v>
       </c>
       <c r="E2" t="n">
-        <v>77.91630000000001</v>
+        <v>82.71259999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>37.5174</v>
+        <v>44.2389</v>
       </c>
       <c r="G2" t="n">
         <v>77.434</v>
@@ -610,13 +610,13 @@
         <v>69.5261</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.316</v>
+        <v>8.202199999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.5163</v>
+        <v>1.2801</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2002999999999999</v>
+        <v>6.9219</v>
       </c>
       <c r="V2" t="n">
         <v>14.288</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>109.1752</v>
+        <v>96.54689999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>71.47020000000001</v>
+        <v>63.0325</v>
       </c>
       <c r="F3" t="n">
-        <v>37.7046</v>
+        <v>33.5147</v>
       </c>
       <c r="G3" t="n">
         <v>34.1045</v>
@@ -688,13 +688,13 @@
         <v>51.3117</v>
       </c>
       <c r="S3" t="n">
-        <v>25.1044</v>
+        <v>12.4765</v>
       </c>
       <c r="T3" t="n">
-        <v>11.1921</v>
+        <v>2.7539</v>
       </c>
       <c r="U3" t="n">
-        <v>13.912</v>
+        <v>9.7224</v>
       </c>
       <c r="V3" t="n">
         <v>28.6188</v>
@@ -721,13 +721,13 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>87.0557</v>
+        <v>79.0226</v>
       </c>
       <c r="E4" t="n">
-        <v>56.0193</v>
+        <v>51.46</v>
       </c>
       <c r="F4" t="n">
-        <v>31.0365</v>
+        <v>27.5626</v>
       </c>
       <c r="G4" t="n">
         <v>42.1603</v>
@@ -766,13 +766,13 @@
         <v>61.4964</v>
       </c>
       <c r="S4" t="n">
-        <v>23.3009</v>
+        <v>15.2679</v>
       </c>
       <c r="T4" t="n">
-        <v>8.818899999999999</v>
+        <v>4.2595</v>
       </c>
       <c r="U4" t="n">
-        <v>14.4822</v>
+        <v>11.0087</v>
       </c>
       <c r="V4" t="n">
         <v>-6.0206</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>50.3674</v>
+        <v>40.8176</v>
       </c>
       <c r="E5" t="n">
-        <v>37.844</v>
+        <v>20.2209</v>
       </c>
       <c r="F5" t="n">
-        <v>12.5232</v>
+        <v>20.5968</v>
       </c>
       <c r="G5" t="n">
-        <v>17.5511</v>
+        <v>26.6194</v>
       </c>
       <c r="H5" t="n">
-        <v>21.768</v>
+        <v>10.5544</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.2171</v>
+        <v>16.0648</v>
       </c>
       <c r="J5" t="n">
-        <v>32.861</v>
+        <v>36.6343</v>
       </c>
       <c r="K5" t="n">
-        <v>26.477</v>
+        <v>18.9223</v>
       </c>
       <c r="L5" t="n">
-        <v>6.383800000000001</v>
+        <v>17.7116</v>
       </c>
       <c r="M5" t="n">
-        <v>-15.3095</v>
+        <v>-10.0153</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.7094</v>
+        <v>-8.3682</v>
       </c>
       <c r="O5" t="n">
-        <v>-10.6008</v>
+        <v>-1.6471</v>
       </c>
       <c r="P5" t="n">
-        <v>11.7509</v>
+        <v>11.7505</v>
       </c>
       <c r="Q5" t="n">
-        <v>-21.9347</v>
+        <v>-23.5013</v>
       </c>
       <c r="R5" t="n">
-        <v>33.6855</v>
+        <v>35.2524</v>
       </c>
       <c r="S5" t="n">
-        <v>31.5023</v>
+        <v>7.718900000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>20.2646</v>
+        <v>2.0042</v>
       </c>
       <c r="U5" t="n">
-        <v>11.2378</v>
+        <v>5.7146</v>
       </c>
       <c r="V5" t="n">
-        <v>-10.437</v>
+        <v>-5.271599999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>6.6536</v>
+        <v>5.0843</v>
       </c>
       <c r="X5" t="n">
-        <v>-17.0907</v>
+        <v>-10.3558</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>47.7065</v>
+        <v>37.7188</v>
       </c>
       <c r="E6" t="n">
-        <v>49.7428</v>
+        <v>40.5289</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0365</v>
+        <v>-2.810099999999999</v>
       </c>
       <c r="G6" t="n">
         <v>28.9549</v>
@@ -922,13 +922,13 @@
         <v>41.1279</v>
       </c>
       <c r="S6" t="n">
-        <v>23.3249</v>
+        <v>13.3371</v>
       </c>
       <c r="T6" t="n">
-        <v>16.4261</v>
+        <v>7.2121</v>
       </c>
       <c r="U6" t="n">
-        <v>6.8989</v>
+        <v>6.1247</v>
       </c>
       <c r="V6" t="n">
         <v>-23.7665</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>38.4085</v>
+        <v>35.592</v>
       </c>
       <c r="E7" t="n">
-        <v>18.9273</v>
+        <v>27.2934</v>
       </c>
       <c r="F7" t="n">
-        <v>19.4811</v>
+        <v>8.298400000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>26.6194</v>
+        <v>17.5511</v>
       </c>
       <c r="H7" t="n">
-        <v>10.5544</v>
+        <v>21.768</v>
       </c>
       <c r="I7" t="n">
-        <v>16.0648</v>
+        <v>-4.2171</v>
       </c>
       <c r="J7" t="n">
-        <v>36.6343</v>
+        <v>32.861</v>
       </c>
       <c r="K7" t="n">
-        <v>18.9223</v>
+        <v>26.477</v>
       </c>
       <c r="L7" t="n">
-        <v>17.7116</v>
+        <v>6.383800000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-10.0153</v>
+        <v>-15.3095</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.3682</v>
+        <v>-4.7094</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6471</v>
+        <v>-10.6008</v>
       </c>
       <c r="P7" t="n">
-        <v>11.7505</v>
+        <v>11.7509</v>
       </c>
       <c r="Q7" t="n">
-        <v>-23.5013</v>
+        <v>-21.9347</v>
       </c>
       <c r="R7" t="n">
-        <v>35.2524</v>
+        <v>33.6855</v>
       </c>
       <c r="S7" t="n">
-        <v>5.309299999999999</v>
+        <v>16.7268</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7105000000000001</v>
+        <v>9.7142</v>
       </c>
       <c r="U7" t="n">
-        <v>4.5991</v>
+        <v>7.0125</v>
       </c>
       <c r="V7" t="n">
-        <v>-5.271599999999999</v>
+        <v>-10.437</v>
       </c>
       <c r="W7" t="n">
-        <v>5.0843</v>
+        <v>6.6536</v>
       </c>
       <c r="X7" t="n">
-        <v>-10.3558</v>
+        <v>-17.0907</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>19.3846</v>
+        <v>30.6783</v>
       </c>
       <c r="E8" t="n">
-        <v>21.6845</v>
+        <v>27.8479</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.300299999999999</v>
+        <v>2.830800000000001</v>
       </c>
       <c r="G8" t="n">
         <v>26.1091</v>
@@ -1078,13 +1078,13 @@
         <v>37.9944</v>
       </c>
       <c r="S8" t="n">
-        <v>-9.6553</v>
+        <v>1.6381</v>
       </c>
       <c r="T8" t="n">
-        <v>-6.2997</v>
+        <v>-0.1366999999999998</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.3559</v>
+        <v>1.7749</v>
       </c>
       <c r="V8" t="n">
         <v>-5.882600000000001</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. MENDÉZ POLLÁN</t>
+          <t>A. CARDITO MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8588</v>
+        <v>2.882600000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0976</v>
+        <v>-8.2217</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2387000000000001</v>
+        <v>11.1047</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5889</v>
+        <v>-0.2462</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1392</v>
+        <v>3.4216</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4497</v>
+        <v>-3.668</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6328</v>
+        <v>20.8018</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5924</v>
+        <v>13.0126</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0404</v>
+        <v>7.789600000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9560999999999999</v>
+        <v>-21.0481</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5468</v>
+        <v>-9.591099999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4093</v>
+        <v>-11.4571</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>6.071099999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1958</v>
+        <v>-31.9229</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1958</v>
+        <v>37.9943</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4863</v>
+        <v>0.8265999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3852</v>
+        <v>-1.128</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1011</v>
+        <v>1.9546</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2166</v>
+        <v>-3.7691</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2754</v>
+        <v>4.0281</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.492</v>
+        <v>-7.797</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. FERRE FERNANDEZ</t>
+          <t>Y. MENDÉZ POLLÁN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.295</v>
+        <v>1.8191</v>
       </c>
       <c r="E10" t="n">
-        <v>1.289</v>
+        <v>1.7906</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006</v>
+        <v>0.02849999999999986</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6802</v>
+        <v>2.5889</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0443</v>
+        <v>2.1392</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3641</v>
+        <v>0.4497</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6166</v>
+        <v>1.6328</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0412</v>
+        <v>1.5924</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5755</v>
+        <v>0.0404</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9364</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0031</v>
+        <v>0.5468</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9396</v>
+        <v>0.4093</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7649</v>
+        <v>0.4467</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6516</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1132</v>
+        <v>0.3685</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5417</v>
+        <v>-1.2166</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5417</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. PULLEIRO GONZALEZ</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6973</v>
+        <v>1.1033</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8083</v>
+        <v>-3.0507</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8892</v>
+        <v>4.1542</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.829</v>
+        <v>-4.2228</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.4349</v>
+        <v>-1.0456</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3942</v>
+        <v>-3.1771</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4405</v>
+        <v>10.5</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.4194</v>
+        <v>6.0644</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.02110000000000001</v>
+        <v>4.4355</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3886</v>
+        <v>-14.7227</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0156</v>
+        <v>-7.1098</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3731</v>
+        <v>-7.6126</v>
       </c>
       <c r="P11" t="n">
-        <v>3.1335</v>
+        <v>6.462899999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1958</v>
+        <v>-15.0802</v>
       </c>
       <c r="R11" t="n">
-        <v>3.3293</v>
+        <v>21.5434</v>
       </c>
       <c r="S11" t="n">
-        <v>1.649</v>
+        <v>-1.7774</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2198</v>
+        <v>-2.005</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4293</v>
+        <v>0.2278999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.651</v>
+        <v>0.6404000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6083</v>
+        <v>3.5348</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.2593</v>
+        <v>-2.8944</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. NIETO FONTAIÑA</t>
+          <t>A. FERRE FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0424</v>
+        <v>1.0193</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0739</v>
+        <v>0.8797</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0318</v>
+        <v>0.1397</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2364999999999995</v>
+        <v>0.6802</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9163</v>
+        <v>1.0443</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.679900000000001</v>
+        <v>-0.3641</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.03420000000000023</v>
+        <v>1.6166</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6976</v>
+        <v>1.0412</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.7319</v>
+        <v>0.5755</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2703</v>
+        <v>-0.9364</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2185</v>
+        <v>0.0031</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05149999999999988</v>
+        <v>-0.9396</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.9584</v>
+        <v>0.3917</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.8545</v>
+        <v>-0.9792</v>
       </c>
       <c r="R12" t="n">
-        <v>4.8961</v>
+        <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4896</v>
+        <v>0.4892</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.01000000000000015</v>
+        <v>0.2423</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4997</v>
+        <v>0.2469</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.8102</v>
+        <v>-0.5417</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.6351</v>
+        <v>-0.5417</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>R. PULLEIRO GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.452900000000001</v>
+        <v>-2.1553</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.483999999999999</v>
+        <v>-1.3465</v>
       </c>
       <c r="F13" t="n">
-        <v>2.031200000000001</v>
+        <v>-0.8089</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.2228</v>
+        <v>-3.829</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0456</v>
+        <v>-3.4349</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.1771</v>
+        <v>-0.3942</v>
       </c>
       <c r="J13" t="n">
-        <v>10.5</v>
+        <v>-2.4405</v>
       </c>
       <c r="K13" t="n">
-        <v>6.0644</v>
+        <v>-2.4194</v>
       </c>
       <c r="L13" t="n">
-        <v>4.4355</v>
+        <v>-0.02110000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.7227</v>
+        <v>-1.3886</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.1098</v>
+        <v>-1.0156</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.6126</v>
+        <v>-0.3731</v>
       </c>
       <c r="P13" t="n">
-        <v>6.462899999999999</v>
+        <v>3.1335</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.0802</v>
+        <v>-0.1958</v>
       </c>
       <c r="R13" t="n">
-        <v>21.5434</v>
+        <v>3.3293</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.333500000000001</v>
+        <v>1.191</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.4385</v>
+        <v>0.6815</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8951</v>
+        <v>0.5094</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6404000000000001</v>
+        <v>-2.651</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5348</v>
+        <v>0.6083</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.8944</v>
+        <v>-3.2593</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CARDITO MARTIN</t>
+          <t>S. NIETO FONTAIÑA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.064400000000001</v>
+        <v>-2.9682</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.8773</v>
+        <v>-4.136500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>7.8126</v>
+        <v>1.1679</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2462</v>
+        <v>0.2364999999999995</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4216</v>
+        <v>1.9163</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.668</v>
+        <v>-1.679900000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>20.8018</v>
+        <v>-0.03420000000000023</v>
       </c>
       <c r="K14" t="n">
-        <v>13.0126</v>
+        <v>1.6976</v>
       </c>
       <c r="L14" t="n">
-        <v>7.789600000000001</v>
+        <v>-1.7319</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.0481</v>
+        <v>0.2703</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.591099999999999</v>
+        <v>0.2185</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.4571</v>
+        <v>0.05149999999999988</v>
       </c>
       <c r="P14" t="n">
-        <v>6.071099999999999</v>
+        <v>-1.9584</v>
       </c>
       <c r="Q14" t="n">
-        <v>-31.9229</v>
+        <v>-6.8545</v>
       </c>
       <c r="R14" t="n">
-        <v>37.9943</v>
+        <v>4.8961</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.1206</v>
+        <v>2.5639</v>
       </c>
       <c r="T14" t="n">
-        <v>-8.783300000000001</v>
+        <v>0.9276000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3372</v>
+        <v>1.6365</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.7691</v>
+        <v>-3.8102</v>
       </c>
       <c r="W14" t="n">
-        <v>4.0281</v>
+        <v>1.8249</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.797</v>
+        <v>-5.6351</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.0585</v>
+        <v>-8.5098</v>
       </c>
       <c r="E15" t="n">
-        <v>-15.9762</v>
+        <v>-13.6493</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9177</v>
+        <v>5.1392</v>
       </c>
       <c r="G15" t="n">
         <v>-5.2711</v>
@@ -1624,13 +1624,13 @@
         <v>10.5754</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.2515</v>
+        <v>0.2970999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.8581</v>
+        <v>0.4692</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.3934</v>
+        <v>-0.1717</v>
       </c>
       <c r="V15" t="n">
         <v>-3.1442</v>
@@ -1657,13 +1657,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>-13.7725</v>
+        <v>-11.1084</v>
       </c>
       <c r="E16" t="n">
-        <v>-14.5171</v>
+        <v>-12.3186</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7445999999999999</v>
+        <v>1.210199999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-5.992800000000001</v>
@@ -1702,13 +1702,13 @@
         <v>22.3266</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1832999999999997</v>
+        <v>2.4808</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.2664</v>
+        <v>-1.0681</v>
       </c>
       <c r="U16" t="n">
-        <v>3.0832</v>
+        <v>3.5487</v>
       </c>
       <c r="V16" t="n">
         <v>-11.5133</v>
@@ -1735,13 +1735,13 @@
         <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>-31.5159</v>
+        <v>-15.5565</v>
       </c>
       <c r="E17" t="n">
-        <v>-41.022</v>
+        <v>-29.6827</v>
       </c>
       <c r="F17" t="n">
-        <v>9.5062</v>
+        <v>14.1261</v>
       </c>
       <c r="G17" t="n">
         <v>-16.088</v>
@@ -1780,13 +1780,13 @@
         <v>33.4899</v>
       </c>
       <c r="S17" t="n">
-        <v>-11.1683</v>
+        <v>4.7908</v>
       </c>
       <c r="T17" t="n">
-        <v>-11.6099</v>
+        <v>-0.2707000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4415000000000001</v>
+        <v>5.0615</v>
       </c>
       <c r="V17" t="n">
         <v>-12.8771</v>
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>393.0814</v>
+        <v>413.854</v>
       </c>
       <c r="E18" t="n">
-        <v>236.2322</v>
+        <v>243.3605</v>
       </c>
       <c r="F18" t="n">
-        <v>156.8482</v>
+        <v>170.4937</v>
       </c>
       <c r="G18" t="n">
         <v>220.789</v>
@@ -1828,7 +1828,7 @@
         <v>140.2803</v>
       </c>
       <c r="I18" t="n">
-        <v>80.5072</v>
+        <v>80.50719999999998</v>
       </c>
       <c r="J18" t="n">
         <v>405.6154</v>
@@ -1843,7 +1843,7 @@
         <v>-184.8276</v>
       </c>
       <c r="N18" t="n">
-        <v>-96.83769999999998</v>
+        <v>-96.8377</v>
       </c>
       <c r="O18" t="n">
         <v>-87.99080000000001</v>
@@ -1858,16 +1858,16 @@
         <v>466.1161</v>
       </c>
       <c r="S18" t="n">
-        <v>65.90309999999999</v>
+        <v>86.67619999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>17.8866</v>
+        <v>25.0143</v>
       </c>
       <c r="U18" t="n">
-        <v>48.0167</v>
+        <v>61.66200000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-47.3543</v>
+        <v>-47.35429999999999</v>
       </c>
       <c r="W18" t="n">
         <v>125.1105</v>
